--- a/Recaptcha/vtu_results_rv.xlsx
+++ b/Recaptcha/vtu_results_rv.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$3:$X$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$3:$R$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -177,7 +177,7 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>9467850</colOff>
+      <colOff>6191250</colOff>
       <row>0</row>
       <rowOff>57150</rowOff>
     </from>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -508,16 +508,10 @@
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="70" customHeight="1">
@@ -539,12 +533,6 @@
       <c r="P1" s="2" t="n"/>
       <c r="Q1" s="2" t="n"/>
       <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
-      <c r="W1" s="2" t="n"/>
-      <c r="X1" s="2" t="n"/>
     </row>
     <row r="2" ht="8" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -565,12 +553,6 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n"/>
-      <c r="V2" s="2" t="n"/>
-      <c r="W2" s="2" t="n"/>
-      <c r="X2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -585,110 +567,80 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>BCS601 - Subject Name</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>BCS601 - Internal Marks</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>BCS601 - External Marks</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>BCS601 - Total Marks</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>BCS601 - Grade</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>BCS601 - Result</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>BCS602 - Subject Name</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>BCS602 - Internal Marks</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>BCS602 - External Marks</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>BCS602 - Total Marks</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>BCS602 - Grade</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>BCS602 - Result</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>BCS613C - Subject Name</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>BCS613C - Internal Marks</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>BCS613C - External Marks</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>BCS613C - Total Marks</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>BCS613C - Grade</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>BCS613C - Result</t>
-        </is>
-      </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>BCV654C - Subject Name</t>
+          <t>Overall Total</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>BCV654C - Internal Marks</t>
+          <t>Overall Max Marks</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>BCV654C - External Marks</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>BCV654C - Total Marks</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>BCV654C - Grade</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>BCV654C - Result</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>Overall Total</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>Overall Max Marks</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
@@ -697,103 +649,79 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>1GD23CS074</t>
+          <t>1GD23CS002</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>P MOHAN</t>
+          <t>ABDUL SHUAIB</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t>CLOUD COMPUTING</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
           <t>MACHINE LEARNING</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>COMPILER DESIGN</t>
-        </is>
-      </c>
       <c r="J4" s="4" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>INTEGRATED WASTE MANAGEMENT FOR A SMART CITY</t>
-        </is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>99</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="S4" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>251</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="W4" s="4" t="n">
-        <v>83.66666666666667</v>
-      </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>83.67%</t>
+        <v>49.5</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>49.50%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:X4"/>
+  <autoFilter ref="A3:R4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/Recaptcha/vtu_results_rv.xlsx
+++ b/Recaptcha/vtu_results_rv.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$3:$R$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$3:$L$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -177,7 +177,7 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>6191250</colOff>
+      <colOff>2914650</colOff>
       <row>0</row>
       <rowOff>57150</rowOff>
     </from>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -502,16 +502,10 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="70" customHeight="1">
@@ -527,12 +521,6 @@
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="2" t="n"/>
       <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
     </row>
     <row r="2" ht="8" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -547,12 +535,6 @@
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -597,50 +579,20 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>BCS602 - Subject Name</t>
+          <t>Overall Total</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>BCS602 - Internal Marks</t>
+          <t>Overall Max Marks</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>BCS602 - External Marks</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>BCS602 - Total Marks</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>BCS602 - Grade</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>BCS602 - Result</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>Overall Total</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>Overall Max Marks</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
@@ -649,12 +601,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>1GD23CS002</t>
+          <t>1GD23CS066</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>ABDUL SHUAIB</t>
+          <t>MONITHA LOKESH K</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -666,62 +618,38 @@
         <v>37</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
           <t>P</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>MACHINE LEARNING</t>
-        </is>
+      <c r="I4" s="4" t="n">
+        <v>56</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>49.50%</t>
+        <v>56.00000000000001</v>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>56.00%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:R4"/>
+  <autoFilter ref="A3:L4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/Recaptcha/vtu_results_rv.xlsx
+++ b/Recaptcha/vtu_results_rv.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$3:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$3:$AD$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -177,7 +177,7 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>2914650</colOff>
+      <colOff>12744450</colOff>
       <row>0</row>
       <rowOff>57150</rowOff>
     </from>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -502,10 +502,28 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="70" customHeight="1">
@@ -521,6 +539,24 @@
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="2" t="n"/>
       <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
     </row>
     <row r="2" ht="8" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -535,6 +571,24 @@
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
+      <c r="W2" s="2" t="n"/>
+      <c r="X2" s="2" t="n"/>
+      <c r="Y2" s="2" t="n"/>
+      <c r="Z2" s="2" t="n"/>
+      <c r="AA2" s="2" t="n"/>
+      <c r="AB2" s="2" t="n"/>
+      <c r="AC2" s="2" t="n"/>
+      <c r="AD2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -579,20 +633,110 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>BCS602 - Subject Name</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>BCS602 - Internal Marks</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>BCS602 - External Marks</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>BCS602 - Total Marks</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>BCS602 - Grade</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>BCS602 - Result</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>BCS613C - Subject Name</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>BCS613C - Internal Marks</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>BCS613C - External Marks</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>BCS613C - Total Marks</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>BCS613C - Grade</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>BCS613C - Result</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>BCV654C - Subject Name</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>BCV654C - Internal Marks</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>BCV654C - External Marks</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>BCV654C - Total Marks</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>BCV654C - Grade</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>BCV654C - Result</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
           <t>Overall Total</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>Overall Max Marks</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="AD3" s="3" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
@@ -601,12 +745,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>1GD23CS066</t>
+          <t>1GD23CS002</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>MONITHA LOKESH K</t>
+          <t>ABDUL SHUAIB</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -618,38 +762,178 @@
         <v>37</v>
       </c>
       <c r="E4" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>MACHINE LEARNING</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="K4" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="inlineStr"/>
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr"/>
+      <c r="Y4" s="4" t="inlineStr"/>
+      <c r="Z4" s="4" t="inlineStr"/>
+      <c r="AA4" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="AB4" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="AC4" s="4" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>49.50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1GD23CS074</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>P MOHAN</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>MACHINE LEARNING</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="I4" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>56.00000000000001</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>56.00%</t>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>COMPILER DESIGN</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>INTEGRATED WASTE MANAGEMENT FOR A SMART CITY</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="n">
+        <v>251</v>
+      </c>
+      <c r="AB5" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="AC5" s="4" t="n">
+        <v>83.66666666666667</v>
+      </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>83.67%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L4"/>
+  <autoFilter ref="A3:AD5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/Recaptcha/vtu_results_rv.xlsx
+++ b/Recaptcha/vtu_results_rv.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$3:$AD$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$3:$X$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -177,7 +177,7 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>12744450</colOff>
+      <colOff>9467850</colOff>
       <row>0</row>
       <rowOff>57150</rowOff>
     </from>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:X5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -514,16 +514,10 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="70" customHeight="1">
@@ -551,12 +545,6 @@
       <c r="V1" s="2" t="n"/>
       <c r="W1" s="2" t="n"/>
       <c r="X1" s="2" t="n"/>
-      <c r="Y1" s="2" t="n"/>
-      <c r="Z1" s="2" t="n"/>
-      <c r="AA1" s="2" t="n"/>
-      <c r="AB1" s="2" t="n"/>
-      <c r="AC1" s="2" t="n"/>
-      <c r="AD1" s="2" t="n"/>
     </row>
     <row r="2" ht="8" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -583,12 +571,6 @@
       <c r="V2" s="2" t="n"/>
       <c r="W2" s="2" t="n"/>
       <c r="X2" s="2" t="n"/>
-      <c r="Y2" s="2" t="n"/>
-      <c r="Z2" s="2" t="n"/>
-      <c r="AA2" s="2" t="n"/>
-      <c r="AB2" s="2" t="n"/>
-      <c r="AC2" s="2" t="n"/>
-      <c r="AD2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -603,140 +585,110 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>BCS601 - Subject Name</t>
+          <t>BCS602 - Subject Name</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>BCS601 - Internal Marks</t>
+          <t>BCS602 - Internal Marks</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>BCS601 - External Marks</t>
+          <t>BCS602 - External Marks</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>BCS601 - Total Marks</t>
+          <t>BCS602 - Total Marks</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>BCS601 - Grade</t>
+          <t>BCS602 - Grade</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>BCS601 - Result</t>
+          <t>BCS602 - Result</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>BCS602 - Subject Name</t>
+          <t>BCS613C - Subject Name</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>BCS602 - Internal Marks</t>
+          <t>BCS613C - Internal Marks</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>BCS602 - External Marks</t>
+          <t>BCS613C - External Marks</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>BCS602 - Total Marks</t>
+          <t>BCS613C - Total Marks</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>BCS602 - Grade</t>
+          <t>BCS613C - Grade</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>BCS602 - Result</t>
+          <t>BCS613C - Result</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>BCS613C - Subject Name</t>
+          <t>BCV654C - Subject Name</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>BCS613C - Internal Marks</t>
+          <t>BCV654C - Internal Marks</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>BCS613C - External Marks</t>
+          <t>BCV654C - External Marks</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>BCS613C - Total Marks</t>
+          <t>BCV654C - Total Marks</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>BCS613C - Grade</t>
+          <t>BCV654C - Grade</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>BCS613C - Result</t>
+          <t>BCV654C - Result</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>BCV654C - Subject Name</t>
+          <t>Overall Total</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>BCV654C - Internal Marks</t>
+          <t>Overall Max Marks</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>BCV654C - External Marks</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>BCV654C - Total Marks</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>BCV654C - Grade</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>BCV654C - Result</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>Overall Total</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr">
-        <is>
-          <t>Overall Max Marks</t>
-        </is>
-      </c>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
@@ -745,98 +697,110 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>1GD23CS002</t>
+          <t>1GD23CS074</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>ABDUL SHUAIB</t>
+          <t>P MOHAN</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>CLOUD COMPUTING</t>
+          <t>MACHINE LEARNING</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
           <t>P</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>MACHINE LEARNING</t>
+          <t>COMPILER DESIGN</t>
         </is>
       </c>
       <c r="J4" s="4" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr"/>
-      <c r="Y4" s="4" t="inlineStr"/>
-      <c r="Z4" s="4" t="inlineStr"/>
-      <c r="AA4" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="AB4" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="AC4" s="4" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>49.50%</t>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>INTEGRATED WASTE MANAGEMENT FOR A SMART CITY</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>251</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>83.66666666666667</v>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>83.67%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1GD23CS074</t>
+          <t>1GD23CS075</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>P MOHAN</t>
+          <t>FETCH FAILED</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -845,95 +809,35 @@
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>MACHINE LEARNING</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>COMPILER DESIGN</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>INTEGRATED WASTE MANAGEMENT FOR A SMART CITY</t>
-        </is>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="X5" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="n">
-        <v>251</v>
-      </c>
-      <c r="AB5" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="AC5" s="4" t="n">
-        <v>83.66666666666667</v>
-      </c>
-      <c r="AD5" s="4" t="inlineStr">
-        <is>
-          <t>83.67%</t>
+        <v>0</v>
+      </c>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AD5"/>
+  <autoFilter ref="A3:X5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/Recaptcha/vtu_results_rv.xlsx
+++ b/Recaptcha/vtu_results_rv.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$3:$X$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$3:$R$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -177,7 +177,7 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>9467850</colOff>
+      <colOff>6191250</colOff>
       <row>0</row>
       <rowOff>57150</rowOff>
     </from>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -508,16 +508,10 @@
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="70" customHeight="1">
@@ -539,12 +533,6 @@
       <c r="P1" s="2" t="n"/>
       <c r="Q1" s="2" t="n"/>
       <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
-      <c r="W1" s="2" t="n"/>
-      <c r="X1" s="2" t="n"/>
     </row>
     <row r="2" ht="8" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -565,12 +553,6 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n"/>
-      <c r="V2" s="2" t="n"/>
-      <c r="W2" s="2" t="n"/>
-      <c r="X2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -585,110 +567,80 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>BCS602 - Subject Name</t>
+          <t>BCS601 - Subject Name</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>BCS602 - Internal Marks</t>
+          <t>BCS601 - Internal Marks</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>BCS602 - External Marks</t>
+          <t>BCS601 - External Marks</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>BCS602 - Total Marks</t>
+          <t>BCS601 - Total Marks</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>BCS602 - Grade</t>
+          <t>BCS601 - Grade</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>BCS602 - Result</t>
+          <t>BCS601 - Result</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>BCS613C - Subject Name</t>
+          <t>BCS613A - Subject Name</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>BCS613C - Internal Marks</t>
+          <t>BCS613A - Internal Marks</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>BCS613C - External Marks</t>
+          <t>BCS613A - External Marks</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>BCS613C - Total Marks</t>
+          <t>BCS613A - Total Marks</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>BCS613C - Grade</t>
+          <t>BCS613A - Grade</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>BCS613C - Result</t>
+          <t>BCS613A - Result</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>BCV654C - Subject Name</t>
+          <t>Overall Total</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>BCV654C - Internal Marks</t>
+          <t>Overall Max Marks</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>BCV654C - External Marks</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>BCV654C - Total Marks</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>BCV654C - Grade</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>BCV654C - Result</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>Overall Total</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>Overall Max Marks</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>percentage</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
@@ -697,147 +649,79 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>1GD23CS074</t>
+          <t>1GD23CS064</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>P MOHAN</t>
+          <t>MOHITH S</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>MACHINE LEARNING</t>
+          <t>CLOUD COMPUTING</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKCHAIN TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>COMPILER DESIGN</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>INTEGRATED WASTE MANAGEMENT FOR A SMART CITY</t>
-        </is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>99</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="S4" s="4" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>251</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="W4" s="4" t="n">
-        <v>83.66666666666667</v>
-      </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>83.67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>1GD23CS075</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>FETCH FAILED</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+        <v>49.5</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>49.50%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:X5"/>
+  <autoFilter ref="A3:R4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/Recaptcha/vtu_results_rv.xlsx
+++ b/Recaptcha/vtu_results_rv.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$3:$R$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$3:$X$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -177,7 +177,7 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>6191250</colOff>
+      <colOff>9467850</colOff>
       <row>0</row>
       <rowOff>57150</rowOff>
     </from>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -508,10 +508,16 @@
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="70" customHeight="1">
@@ -533,6 +539,12 @@
       <c r="P1" s="2" t="n"/>
       <c r="Q1" s="2" t="n"/>
       <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
     </row>
     <row r="2" ht="8" customHeight="1">
       <c r="A2" s="2" t="n"/>
@@ -553,6 +565,12 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
+      <c r="W2" s="2" t="n"/>
+      <c r="X2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -567,80 +585,110 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>BCS601 - Subject Name</t>
+          <t>BCS602 - Subject Name</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>BCS601 - Internal Marks</t>
+          <t>BCS602 - Internal Marks</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>BCS601 - External Marks</t>
+          <t>BCS602 - External Marks</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>BCS601 - Total Marks</t>
+          <t>BCS602 - Total Marks</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>BCS601 - Grade</t>
+          <t>BCS602 - Grade</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>BCS601 - Result</t>
+          <t>BCS602 - Result</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>BCS613A - Subject Name</t>
+          <t>BCS613C - Subject Name</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>BCS613A - Internal Marks</t>
+          <t>BCS613C - Internal Marks</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>BCS613A - External Marks</t>
+          <t>BCS613C - External Marks</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>BCS613A - Total Marks</t>
+          <t>BCS613C - Total Marks</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>BCS613A - Grade</t>
+          <t>BCS613C - Grade</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>BCS613A - Result</t>
+          <t>BCS613C - Result</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
+          <t>BCV654C - Subject Name</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>BCV654C - Internal Marks</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>BCV654C - External Marks</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>BCV654C - Total Marks</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>BCV654C - Grade</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>BCV654C - Result</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
           <t>Overall Total</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>Overall Max Marks</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>Percentage</t>
         </is>
@@ -649,79 +697,103 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>1GD23CS064</t>
+          <t>1GD23CS074</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>MOHITH S</t>
+          <t>P MOHAN</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>CLOUD COMPUTING</t>
+          <t>MACHINE LEARNING</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F4" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>COMPILER DESIGN</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKCHAIN TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="n">
+      <c r="K4" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>INTEGRATED WASTE MANAGEMENT FOR A SMART CITY</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>49.50%</t>
+      <c r="U4" s="4" t="n">
+        <v>251</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>83.66666666666667</v>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>83.67%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:R4"/>
+  <autoFilter ref="A3:X4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
